--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1956,6 +1956,512 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:22</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:22</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:22</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:27</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:27</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:30</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:32</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:32</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:32</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:33</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2462,6 +2462,510 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:10</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:10</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:10</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:11</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:12</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:12</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:12</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:12</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:13</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:13</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:15</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:18</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:18</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:18</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:18</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2966,6 +2966,510 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:03</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:04</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:04</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:04</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:04</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:05</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:05</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:05</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:05</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:05</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:06</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:06</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:06</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:06</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:07</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:09</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:11</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3470,6 +3470,512 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:03</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:03</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:04</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:04</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:04</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:04</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:05</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:05</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:05</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:05</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:09</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:10</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:10</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:12</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:15</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:15</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:15</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:15</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,510 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:36</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:37</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:37</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:37</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:37</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:37</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:38</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:38</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:38</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:38</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:38</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:39</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:39</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:39</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:39</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:42</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:44</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:45</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:45</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-18 11:45</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,6 +1452,510 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:08</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:08</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:08</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:08</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:09</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:09</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:09</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:11</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:14</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:14</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:14</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:14</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1956,6 +1956,510 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:22</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:22</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:22</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:23</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:23</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:23</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:23</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:24</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:24</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:24</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:24</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:24</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:27</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:30</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:30</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:30</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:30</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2460,6 +2460,510 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:56</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:56</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:57</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:57</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:57</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:57</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:57</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:58</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:58</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:58</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:58</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:59</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:59</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:59</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-21 07:59</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-21 08:02</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-21 08:04</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-21 08:05</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-21 08:05</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-21 08:05</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2964,6 +2964,510 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:12</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:12</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:12</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:12</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:12</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:13</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:13</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:13</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:13</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:14</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:14</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:14</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:14</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:14</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:17</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:19</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:19</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:20</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:20</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3468,6 +3468,510 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:01</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:01</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:01</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:02</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:02</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:02</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:02</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:02</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:02</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:03</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:03</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:03</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:03</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:06</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:08</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:08</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:09</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:09</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3972,6 +3972,510 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:21</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:21</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:21</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:21</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:21</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:22</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:22</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:22</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:22</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:23</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:23</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:23</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:23</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:23</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:24</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:29</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:29</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:29</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:29</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4476,6 +4476,510 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:21</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:21</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:21</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:22</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:22</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:22</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:22</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:23</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:23</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:23</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:23</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:23</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:24</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:24</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:24</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:29</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:29</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:29</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:30</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4980,6 +4980,510 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:24</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:24</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:25</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:25</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:25</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:25</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:25</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:27</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:27</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:27</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:27</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:30</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:32</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:32</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:33</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:33</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5484,6 +5484,510 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:41</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:41</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:41</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:42</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:42</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:42</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:42</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:43</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:43</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:43</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:43</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:43</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:44</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:44</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:44</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:47</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:49</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:49</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:49</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-26 11:50</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5988,6 +5988,510 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:12</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:12</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:12</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:13</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:13</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:13</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:13</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:14</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:14</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:14</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:14</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:15</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:15</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:15</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:15</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:18</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:20</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:21</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:21</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-27 12:21</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6492,6 +6492,510 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:28</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:28</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C243" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:28</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:28</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:28</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:29</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:29</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:29</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:29</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:29</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:30</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C252" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:30</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:30</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C254" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:30</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C255" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:31</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:33</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:35</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:36</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C259" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:36</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:36</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C261" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,510 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:08</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:09</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:09</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:09</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,6 +1452,514 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:22</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:28</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:28</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:28</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:28</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:29</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:29</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:29</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:29</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:29</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:30</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:32</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:35</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:35</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:35</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:35</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1960,6 +1960,514 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:08</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:08</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:08</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:11</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:11</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:13</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:13</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:13</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:13</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:16</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:18</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:18</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:19</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2468,6 +2468,514 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:51</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:53</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:54</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:54</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:56</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:56</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:57</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:57</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:57</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:57</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:58</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:58</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:58</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:58</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-03 11:59</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:01</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:04</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:04</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:04</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:04</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,6 +2976,514 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:04</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:06</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:06</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:07</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:10</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:10</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:10</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:10</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:11</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:11</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:11</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:11</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:14</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:16</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:17</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:17</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-04 12:17</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3484,6 +3484,516 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:28</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:29</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:29</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:31</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:31</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:32</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:32</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:32</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:32</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:32</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:33</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:33</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:33</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:33</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:36</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:38</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:41</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:41</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:41</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3994,6 +3994,516 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:25</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:25</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:28</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:28</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:28</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:29</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:29</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:30</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:30</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:30</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:30</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:30</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:31</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:33</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:36</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:38</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:38</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:39</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +4504,516 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:51</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:53</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:53</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:54</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:56</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:56</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:57</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:57</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:57</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:57</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:57</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:58</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:58</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:58</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:58</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:01</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:03</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:06</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:06</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:06</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5014,6 +5014,516 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:45</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:48</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:48</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:48</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:50</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:51</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:51</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:51</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:51</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:52</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:52</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:52</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:52</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:52</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:53</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:55</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:57</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5524,6 +5524,516 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:22</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:25</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:25</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:25</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:28</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:28</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:28</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:28</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:28</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:29</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:29</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:29</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:29</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:29</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:30</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:32</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:34</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:37</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:37</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:38</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6034,6 +6034,516 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:23</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:25</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:25</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:25</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:28</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:28</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:28</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:29</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:29</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:29</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:29</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:30</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:30</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:30</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:30</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:33</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:35</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:38</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:38</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-10 12:38</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6544,6 +6544,516 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:44</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:46</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:46</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:47</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:49</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:49</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:49</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:50</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:50</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:50</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:50</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C252" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:51</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:51</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C254" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:51</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C255" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:51</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:54</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:56</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:59</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:59</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-10-11 12:59</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C261" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:E281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7054,6 +7054,516 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:01</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C262" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:04</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:04</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C264" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:04</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C265" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:07</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:07</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C267" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:07</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C268" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:08</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C269" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:08</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C270" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:08</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C271" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:08</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:08</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C273" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:09</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C274" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:09</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C275" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:09</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C276" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:12</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:14</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:17</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:17</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C280" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:17</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C281" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E281"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7564,6 +7564,516 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:09</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C282" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:11</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:12</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C284" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:12</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C285" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:14</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:15</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C287" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:15</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C288" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:15</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C289" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:15</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C290" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:15</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C291" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:16</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C292" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:16</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C293" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:16</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C294" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:16</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C295" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:16</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C296" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:19</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:21</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:24</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:24</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C300" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:24</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C301" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8074,6 +8074,516 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:25</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C302" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:28</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:28</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C304" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:28</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C305" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:31</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:31</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C307" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:31</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:31</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C309" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:32</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C310" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:32</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C311" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:32</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C312" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:32</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C313" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:33</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C314" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:33</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C315" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:33</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C316" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:36</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:38</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:41</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:41</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C320" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:41</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C321" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8584,6 +8584,516 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:08</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C322" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:11</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:11</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C324" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:11</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C325" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:14</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:14</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C327" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:14</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C328" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:15</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C329" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:15</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C330" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:15</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C331" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:15</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C332" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:15</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C333" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:16</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C334" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:16</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C335" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:16</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C336" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:19</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:21</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:23</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:24</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C340" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:24</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C341" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9094,6 +9094,518 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:55</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C342" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:58</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:58</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C344" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:58</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C345" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:01</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C347" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:01</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C348" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:01</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C349" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:01</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C350" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:02</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C351" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:02</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C352" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:02</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C353" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:02</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C354" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:05</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C355" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:07</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:10</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:12</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:14</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:15</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C360" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:15</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C361" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E361"/>
+  <dimension ref="A1:E381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9606,6 +9606,518 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-10-17 10:56</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C362" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-10-17 10:59</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-10-17 10:59</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C364" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-10-17 10:59</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C365" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:02</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:02</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C367" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:02</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C368" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:02</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C369" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:03</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C370" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:03</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C371" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:03</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C372" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:03</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C373" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:04</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C374" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:04</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C375" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:06</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:09</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:11</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:14</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:14</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C380" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:14</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C381" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E381"/>
+  <dimension ref="A1:E401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10118,6 +10118,518 @@
         </is>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:11</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C382" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:14</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:14</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C384" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:14</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C385" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:17</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:17</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C387" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:17</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C388" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:17</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C389" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:18</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C390" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:18</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C391" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:18</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C392" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:18</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C393" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:18</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C394" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:19</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C395" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:21</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:24</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:26</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:29</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:29</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C400" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:29</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C401" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E401"/>
+  <dimension ref="A1:E421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10630,6 +10630,518 @@
         </is>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:44</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C402" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:47</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:47</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C404" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:47</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C405" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:50</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:50</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C407" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:50</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C408" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:50</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C409" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:50</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C410" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:51</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C411" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:51</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C412" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:51</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C413" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:51</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C414" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:51</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C415" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:54</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:56</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:59</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:01</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:02</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C420" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:02</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C421" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E421"/>
+  <dimension ref="A1:E441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11142,6 +11142,518 @@
         </is>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:25</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C422" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:27</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:28</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C424" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:28</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C425" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:30</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:31</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C427" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:31</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C428" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:31</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C429" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:31</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C430" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:31</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C431" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:32</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C432" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:32</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C433" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:32</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C434" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:32</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C435" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:35</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:37</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:40</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:42</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:42</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C440" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:43</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C441" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E441"/>
+  <dimension ref="A1:E461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11654,6 +11654,518 @@
         </is>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:30</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C442" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:33</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:33</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C444" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:33</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C445" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:36</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:36</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C447" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:36</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C448" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:36</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C449" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:37</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C450" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:37</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C451" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:37</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C452" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:37</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C453" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:38</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C454" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:38</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C455" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:40</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:43</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:45</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:48</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:48</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C460" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:48</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C461" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E461"/>
+  <dimension ref="A1:E481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12166,6 +12166,520 @@
         </is>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:36</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C462" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:39</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:39</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C464" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:39</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C465" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:41</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:42</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C467" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:42</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C468" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:42</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C469" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:42</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C470" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:45</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C471" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:45</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C472" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:45</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C473" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:46</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C474" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:46</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C475" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:49</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:51</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:54</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:56</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:56</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C480" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:59</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E481"/>
+  <dimension ref="A1:E501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12680,6 +12680,518 @@
         </is>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:21</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C482" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:24</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:24</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C484" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:24</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C485" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:27</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:27</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C487" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:27</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C488" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:27</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C489" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:28</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C490" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:28</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C491" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:28</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C492" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:28</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C493" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:29</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C494" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:29</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C495" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:31</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:34</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:36</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:39</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:39</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C500" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:39</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C501" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E501"/>
+  <dimension ref="A1:E521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13192,6 +13192,518 @@
         </is>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:17</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C502" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:20</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:20</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C504" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:20</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C505" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:23</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:23</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C507" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:23</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C508" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:23</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C509" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:24</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C510" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:24</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C511" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:24</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C512" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:24</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C513" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:24</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C514" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:25</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C515" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:27</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:30</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:32</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:35</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:35</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C520" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-10-24 11:35</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C521" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E521"/>
+  <dimension ref="A1:E541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13704,6 +13704,518 @@
         </is>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:32</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C522" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:34</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:34</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C524" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:35</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C525" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:37</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:37</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C527" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:38</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C528" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:38</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C529" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:38</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C530" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:38</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C531" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:38</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C532" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:39</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C533" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:39</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C534" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:39</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C535" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:41</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:44</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:46</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:49</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:49</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C540" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:49</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C541" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E541"/>
+  <dimension ref="A1:E561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14216,6 +14216,518 @@
         </is>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:14</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C542" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:17</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:17</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C544" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:17</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C545" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:20</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:20</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C547" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:20</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C548" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:20</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C549" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:20</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C550" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:21</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C551" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:21</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C552" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:21</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C553" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:21</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C554" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:21</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C555" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:24</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:26</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:29</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:31</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:32</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C560" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:32</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C561" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E561"/>
+  <dimension ref="A1:E581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14728,6 +14728,518 @@
         </is>
       </c>
     </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:02</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C562" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:04</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:04</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C564" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:05</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C565" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:07</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:07</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C567" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:08</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C568" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:08</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C569" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:08</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C570" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:08</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C571" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:09</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C572" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:09</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C573" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:09</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C574" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:09</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C575" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:12</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:14</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:17</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:19</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:20</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C580" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:20</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C581" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E581"/>
+  <dimension ref="A1:E601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15240,6 +15240,518 @@
         </is>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:20</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C582" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:22</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:22</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C584" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:23</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C585" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:25</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:25</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C587" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:25</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C588" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:26</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C589" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:26</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C590" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:26</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C591" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:26</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C592" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:26</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C593" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:27</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C594" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:27</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C595" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:29</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:32</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:34</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:37</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:37</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C600" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:37</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C601" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E601"/>
+  <dimension ref="A1:E621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15752,6 +15752,518 @@
         </is>
       </c>
     </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:58</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C602" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:00</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:00</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C604" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:00</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C605" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:03</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:03</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C607" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:03</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C608" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:04</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C609" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:04</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C610" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:04</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C611" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:04</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C612" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:04</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C613" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:05</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C614" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:05</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C615" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:07</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:10</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:12</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:15</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:15</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C620" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:15</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C621" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E621"/>
+  <dimension ref="A1:E641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16264,6 +16264,518 @@
         </is>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-10-31 09:58</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C622" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:01</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C624" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:01</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C625" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:03</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:04</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C627" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:04</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C628" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:04</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C629" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:04</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C630" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:05</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C631" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:05</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C632" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:05</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C633" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:05</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C634" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:06</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C635" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:08</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:11</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:13</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:16</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:16</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C640" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:16</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C641" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
